--- a/cosmos-graph/reports/Instrument_Parent_Chain.xlsx
+++ b/cosmos-graph/reports/Instrument_Parent_Chain.xlsx
@@ -469,7 +469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-12 22:03</t>
+          <t>Generated: 2026-08-23 19:04</t>
         </is>
       </c>
     </row>
@@ -570,13 +570,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="49" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -9308,52 +9308,52 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C123623</t>
+          <t>C123621</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Metabolic Response</t>
+          <t>Disease Recurrence Indicator</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C93645</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Recurrence Indicator</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C25180</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Indicator</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>C123623 &gt; C50995</t>
+          <t>C123621 &gt; C93645 &gt; C25180</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C123627</t>
+          <t>C123623</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Radiologic Response</t>
+          <t>Metabolic Response</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9381,39 +9381,39 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>C123627 &gt; C50995</t>
+          <t>C123623 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C124703</t>
+          <t>C123627</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tanner Scale Boy Version</t>
+          <t>Radiologic Response</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Tanner Scale</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tanner Scale</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -9421,19 +9421,19 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C124703 &gt; C82394</t>
+          <t>C123627 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C124704</t>
+          <t>C124703</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>Tanner Scale Boy Version</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9461,59 +9461,59 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>C124704 &gt; C82394</t>
+          <t>C124703 &gt; C82394</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C124716</t>
+          <t>C124704</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy - Genitalia Stages</t>
+          <t>Tanner Scale Girl Version</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>C124689</t>
+          <t>C82394</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy Clinical Classification Question</t>
+          <t>Tanner Scale</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C82394</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Tanner Scale</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>C124716 &gt; C124689 &gt; C211913 &gt; C91102</t>
+          <t>C124704 &gt; C82394</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C124717</t>
+          <t>C124716</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy - Pubic Hair Stages</t>
+          <t>Tanner Scale-Boy - Genitalia Stages</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9541,29 +9541,29 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C124717 &gt; C124689 &gt; C211913 &gt; C91102</t>
+          <t>C124716 &gt; C124689 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C124718</t>
+          <t>C124717</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl - Breast Stages</t>
+          <t>Tanner Scale-Boy - Pubic Hair Stages</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>C124690</t>
+          <t>C124689</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl Clinical Classification Question</t>
+          <t>Tanner Scale-Boy Clinical Classification Question</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -9581,19 +9581,19 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>C124718 &gt; C124690 &gt; C211913 &gt; C91102</t>
+          <t>C124717 &gt; C124689 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C124719</t>
+          <t>C124718</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl - Pubic Hair Stages</t>
+          <t>Tanner Scale-Girl - Breast Stages</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9621,139 +9621,139 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>C124719 &gt; C124690 &gt; C211913 &gt; C91102</t>
+          <t>C124718 &gt; C124690 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C132532</t>
+          <t>C124719</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Combat Exposure Scale Questionnaire</t>
+          <t>Tanner Scale-Girl - Pubic Hair Stages</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C124690</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Tanner Scale-Girl Clinical Classification Question</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>C132532 &gt; C91105</t>
+          <t>C124719 &gt; C124690 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C132556</t>
+          <t>C125755</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CES - Ever Combat Patrols or Dangerous Duty</t>
+          <t>AJCC Cancer Staging Manual 7th Edition</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>C132527</t>
+          <t>C177561</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>CES Questionnaire Question</t>
+          <t>AJCC Cancer Staging Manual</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>C132556 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C125755 &gt; C177561 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C132557</t>
+          <t>C132532</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CES - Were You Ever Under Enemy Fire</t>
+          <t>Combat Exposure Scale Questionnaire</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>C132527</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>CES Questionnaire Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>C132557 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132532 &gt; C91105</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C132558</t>
+          <t>C132556</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>CES - Ever Surrounded by the Enemy</t>
+          <t>CES - Ever Combat Patrols or Dangerous Duty</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9781,19 +9781,19 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>C132558 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132556 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C132559</t>
+          <t>C132557</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CES - Soldiers in Unit Killed (KIA), Wounded, Missing (MIA)</t>
+          <t>CES - Were You Ever Under Enemy Fire</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9821,19 +9821,19 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>C132559 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132557 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C132560</t>
+          <t>C132558</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CES - How Often Fire Rounds at Enemy</t>
+          <t>CES - Ever Surrounded by the Enemy</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9861,19 +9861,19 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>C132560 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132558 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C132561</t>
+          <t>C132559</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CES - See Someone Hit by Rounds</t>
+          <t>CES - Soldiers in Unit Killed (KIA), Wounded, Missing (MIA)</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9901,19 +9901,19 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>C132561 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132559 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C132562</t>
+          <t>C132560</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CES - In Danger of Being Injured or Killed</t>
+          <t>CES - How Often Fire Rounds at Enemy</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9941,119 +9941,119 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>C132562 &gt; C132527 &gt; C211913 &gt; C91102</t>
+          <t>C132560 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C135477</t>
+          <t>C132561</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Bone Marrow Disease Involvement Indicator</t>
+          <t>CES - See Someone Hit by Rounds</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>C181043</t>
+          <t>C132527</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Clinical Findings Indicator</t>
+          <t>CES Questionnaire Question</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>C181043</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Clinical Findings Indicator</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>C135477 &gt; C181043</t>
+          <t>C132561 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C135478</t>
+          <t>C132562</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Clinical Performance Status</t>
+          <t>CES - In Danger of Being Injured or Killed</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>C171082</t>
+          <t>C132527</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Medical Status</t>
+          <t>CES Questionnaire Question</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>C171082</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Medical Status</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>C135478 &gt; C171082</t>
+          <t>C132562 &gt; C132527 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C135480</t>
+          <t>C135477</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Non-Target Enhancing Lesion Response</t>
+          <t>Bone Marrow Disease Involvement Indicator</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C181043</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical Findings Indicator</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C181043</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical Findings Indicator</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -10061,39 +10061,39 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>C135480 &gt; C50995</t>
+          <t>C135477 &gt; C181043</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C135481</t>
+          <t>C135478</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Non-Target Non-Enhancing Lesion Response</t>
+          <t>Clinical Performance Status</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C171082</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Medical Status</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C171082</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Medical Status</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -10101,19 +10101,19 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>C135481 &gt; C50995</t>
+          <t>C135478 &gt; C171082</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C135482</t>
+          <t>C135480</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Disease Response in Spleen</t>
+          <t>Non-Target Enhancing Lesion Response</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10141,39 +10141,39 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>C135482 &gt; C50995</t>
+          <t>C135480 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C135483</t>
+          <t>C135481</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Steroid Use Status</t>
+          <t>Non-Target Non-Enhancing Lesion Response</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>C83430</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Substance Use Status</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>C83430</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Substance Use Status</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -10181,39 +10181,39 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>C135483 &gt; C83430</t>
+          <t>C135481 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C135738</t>
+          <t>C135482</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Clinical Global Impression Generic Modification Version Questionnaire</t>
+          <t>Disease Response in Spleen</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -10221,39 +10221,39 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>C135738 &gt; C91105</t>
+          <t>C135482 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C135739</t>
+          <t>C135483</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Patient Global Impression Generic Modification Version Questionnaire</t>
+          <t>Steroid Use Status</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C83430</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Substance Use Status</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C83430</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Substance Use Status</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -10261,99 +10261,99 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>C135739 &gt; C91105</t>
+          <t>C135483 &gt; C83430</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C135814</t>
+          <t>C135738</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version - Severity</t>
+          <t>Clinical Global Impression Generic Modification Version Questionnaire</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>C135705</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version Questionnaire Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>C135814 &gt; C135705 &gt; C211913 &gt; C91102</t>
+          <t>C135738 &gt; C91105</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C135815</t>
+          <t>C135739</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version - Change</t>
+          <t>Patient Global Impression Generic Modification Version Questionnaire</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>C135705</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version Questionnaire Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>C135815 &gt; C135705 &gt; C211913 &gt; C91102</t>
+          <t>C135739 &gt; C91105</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C135816</t>
+          <t>C135814</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version - Improvement</t>
+          <t>CGI Generic Modification Version - Severity</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10381,29 +10381,29 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C135816 &gt; C135705 &gt; C211913 &gt; C91102</t>
+          <t>C135814 &gt; C135705 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C135817</t>
+          <t>C135815</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version - Severity</t>
+          <t>CGI Generic Modification Version - Change</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>C135706</t>
+          <t>C135705</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version Questionnaire Question</t>
+          <t>CGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -10421,29 +10421,29 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>C135817 &gt; C135706 &gt; C211913 &gt; C91102</t>
+          <t>C135815 &gt; C135705 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C135818</t>
+          <t>C135816</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version - Change</t>
+          <t>CGI Generic Modification Version - Improvement</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>C135706</t>
+          <t>C135705</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version Questionnaire Question</t>
+          <t>CGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -10461,19 +10461,19 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>C135818 &gt; C135706 &gt; C211913 &gt; C91102</t>
+          <t>C135816 &gt; C135705 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C135819</t>
+          <t>C135817</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version - Improvement</t>
+          <t>PGI Generic Modification Version - Severity</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10501,109 +10501,109 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>C135819 &gt; C135706 &gt; C211913 &gt; C91102</t>
+          <t>C135817 &gt; C135706 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C142362</t>
+          <t>C135818</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>New Lesion Indicator</t>
+          <t>PGI Generic Modification Version - Change</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>C181043</t>
+          <t>C135706</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Clinical Findings Indicator</t>
+          <t>PGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>C181043</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Clinical Findings Indicator</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>C142362 &gt; C181043</t>
+          <t>C135818 &gt; C135706 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C147589</t>
+          <t>C135819</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ATLAS Score Clinical Classification</t>
+          <t>PGI Generic Modification Version - Improvement</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C135706</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>PGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>C147589 &gt; C118969</t>
+          <t>C135819 &gt; C135706 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C147843</t>
+          <t>C141696</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ATLAS - Age</t>
+          <t>AJCC v7 - Primary Tumor (T)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -10617,33 +10617,33 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>C147843 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C141696 &gt; C141675 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C147844</t>
+          <t>C141697</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ATLAS - Treatment With Antibiotics</t>
+          <t>AJCC v7 - Regional Lymph Nodes (N)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -10657,33 +10657,33 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>C147844 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C141697 &gt; C141675 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C147845</t>
+          <t>C141698</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ATLAS - Leukocyte Count</t>
+          <t>AJCC v7 - Distant Metastasis (M)</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -10697,33 +10697,33 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>C147845 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C141698 &gt; C141675 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C147846</t>
+          <t>C141699</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ATLAS - Albumin</t>
+          <t>AJCC v7 - Anatomic Stage</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -10737,113 +10737,113 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>C147846 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C141699 &gt; C141675 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C147847</t>
+          <t>C142362</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ATLAS - Serum Creatinine</t>
+          <t>New Lesion Indicator</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C181043</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>Clinical Findings Indicator</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C181043</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical Findings Indicator</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>C147847 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C142362 &gt; C181043</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C147848</t>
+          <t>C147589</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ATLAS - Score</t>
+          <t>ATLAS Score Clinical Classification</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>C147848 &gt; C147551 &gt; C211913 &gt; C91102</t>
+          <t>C147589 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C155646</t>
+          <t>C147843</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HAMA - Total Score</t>
+          <t>ATLAS - Age</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>C101876</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>HAMA Questionnaire Question</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10861,149 +10861,149 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>C155646 &gt; C101876 &gt; C211913 &gt; C91102</t>
+          <t>C147843 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C156564</t>
+          <t>C147844</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Anatomic Response</t>
+          <t>ATLAS - Treatment With Antibiotics</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>C156564 &gt; C50995</t>
+          <t>C147844 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C191036</t>
+          <t>C147845</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification</t>
+          <t>ATLAS - Leukocyte Count</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>C191036 &gt; C118969</t>
+          <t>C147845 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C191039</t>
+          <t>C147846</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Rutgeerts Score Clinical Classification</t>
+          <t>ATLAS - Albumin</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>C191039 &gt; C118969</t>
+          <t>C147846 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C191044</t>
+          <t>C147847</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HBI - General Well-being</t>
+          <t>ATLAS - Serum Creatinine</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -11021,29 +11021,29 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>C191044 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C147847 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C191045</t>
+          <t>C147848</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HBI - Abdominal Pain</t>
+          <t>ATLAS - Score</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -11061,29 +11061,29 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>C191045 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C147848 &gt; C147551 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C191046</t>
+          <t>C155646</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HBI - Number Liquid Stools</t>
+          <t>HAMA - Total Score</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C101876</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>HAMA Questionnaire Question</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -11101,69 +11101,69 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>C191046 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C155646 &gt; C101876 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C191047</t>
+          <t>C156564</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HBI - Abdominal Mass</t>
+          <t>Anatomic Response</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>C191047 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C156564 &gt; C50995</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C191048</t>
+          <t>C176205</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HBI - Complication: Arthralgia</t>
+          <t>AJCC v7 - Residual Tumor (R)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11177,183 +11177,183 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>C191048 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C176205 &gt; C141675 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C191049</t>
+          <t>C177561</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HBI - Complication: Uveitis</t>
+          <t>AJCC Cancer Staging Manual</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>C191049 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C177561 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C191050</t>
+          <t>C191036</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HBI - Complication: Erythema Nodosum</t>
+          <t>Harvey-Bradshaw Index Clinical Classification</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>C191050 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191036 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C191051</t>
+          <t>C191039</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HBI - Complication: Aphthous Ulcers</t>
+          <t>Rutgeerts Score Clinical Classification</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>C191051 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191039 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C191052</t>
+          <t>C191040</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HBI - Complication: Pyoderma Gangrenosum</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>C191052 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191040 &gt; C118969</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C191053</t>
+          <t>C191044</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HBI - Complication: Anal Fissures</t>
+          <t>HBI - General Well-being</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11381,19 +11381,19 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>C191053 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191044 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C191054</t>
+          <t>C191045</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HBI - Complication: New Fistula</t>
+          <t>HBI - Abdominal Pain</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -11421,19 +11421,19 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>C191054 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191045 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C191055</t>
+          <t>C191046</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HBI - Complication: Abscess</t>
+          <t>HBI - Number Liquid Stools</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -11461,19 +11461,19 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>C191055 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191046 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C191056</t>
+          <t>C191047</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HBI - Total Score</t>
+          <t>HBI - Abdominal Mass</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -11501,29 +11501,29 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>C191056 &gt; C190943 &gt; C211913 &gt; C91102</t>
+          <t>C191047 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C191060</t>
+          <t>C191048</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MVAI - Extension</t>
+          <t>HBI - Complication: Arthralgia</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -11541,29 +11541,29 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>C191060 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191048 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C191061</t>
+          <t>C191049</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MVAI - Hyperintensity T2-weighted Images</t>
+          <t>HBI - Complication: Uveitis</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -11581,29 +11581,29 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>C191061 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191049 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C191062</t>
+          <t>C191050</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MVAI - Rectal Wall Involvement</t>
+          <t>HBI - Complication: Erythema Nodosum</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11621,29 +11621,29 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>C191062 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191050 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C191063</t>
+          <t>C191051</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MVAI - Inflammatory Mass</t>
+          <t>HBI - Complication: Aphthous Ulcers</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11661,29 +11661,29 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>C191063 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191051 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C191064</t>
+          <t>C191052</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MVAI - Dominant Feature</t>
+          <t>HBI - Complication: Pyoderma Gangrenosum</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -11701,29 +11701,29 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>C191064 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191052 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C191065</t>
+          <t>C191053</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MVAI - Total Score</t>
+          <t>HBI - Complication: Anal Fissures</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11741,29 +11741,29 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>C191065 &gt; C190945 &gt; C211913 &gt; C91102</t>
+          <t>C191053 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C191153</t>
+          <t>C191054</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Rutgeerts Score - Rutgeerts Score</t>
+          <t>HBI - Complication: New Fistula</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>C190946</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11781,29 +11781,29 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>C191153 &gt; C190946 &gt; C211913 &gt; C91102</t>
+          <t>C191054 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C208544</t>
+          <t>C191055</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CDISC ADAS-Cog - Total Score</t>
+          <t>HBI - Complication: Abscess</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>C100106</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ADAS-Cog CDISC Version Functional Test Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11821,421 +11821,1421 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>C208544 &gt; C100106 &gt; C211913 &gt; C91102</t>
+          <t>C191055 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C222259</t>
+          <t>C191056</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Cognitive Assessment Tool</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
+          <t>HBI - Total Score</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>C190943</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>C222259</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Cognitive Assessment Tool</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>C222259</t>
+          <t>C191056 &gt; C190943 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C222260</t>
+          <t>C191060</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Clinical or Research Functional Assessment Tool</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
+          <t>MVAI - Extension</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>C190945</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>C222260</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Clinical or Research Functional Assessment Tool</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>C222260</t>
+          <t>C191060 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C191061</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Tanner Scale</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
+          <t>MVAI - Hyperintensity T2-weighted Images</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>C190945</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tanner Scale</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C191061 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C94534</t>
+          <t>C191062</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Response in Target Lesion</t>
+          <t>MVAI - Rectal Wall Involvement</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C190945</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>C94534 &gt; C50995</t>
+          <t>C191062 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C94535</t>
+          <t>C191063</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Response in Non-Target Lesion</t>
+          <t>MVAI - Inflammatory Mass</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C190945</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>C94535 &gt; C50995</t>
+          <t>C191063 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C94536</t>
+          <t>C191064</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Best Overall Response</t>
+          <t>MVAI - Dominant Feature</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C190945</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>C94536 &gt; C50995</t>
+          <t>C191064 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C96613</t>
+          <t>C191065</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Overall Response</t>
+          <t>MVAI - Total Score</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C190945</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>C96613 &gt; C50995</t>
+          <t>C191065 &gt; C190945 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>NEW_LZZT1</t>
+          <t>C191066</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey -  Patch Appearance</t>
+          <t>PASI Fredriksson Version - Head: Erythema/Redness</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>NEW_LZZT</t>
+          <t>C190947</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>NEW_LZZT1 &gt; NEW_LZZT &gt; C91105</t>
+          <t>C191066 &gt; C190947 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>NEW_LZZT2</t>
+          <t>C191067</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey -  Patch Size</t>
+          <t>PASI Fredriksson Version - Head: Thickness/Induration</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>NEW_LZZT</t>
+          <t>C190947</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>NEW_LZZT2 &gt; NEW_LZZT &gt; C91105</t>
+          <t>C191067 &gt; C190947 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>NEW_LZZT3</t>
+          <t>C191068</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey -  Patch Durability</t>
+          <t>PASI Fredriksson Version - Head: Desquamation/Scaling</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>NEW_LZZT</t>
+          <t>C190947</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>NEW_LZZT3 &gt; NEW_LZZT &gt; C91105</t>
+          <t>C191068 &gt; C190947 &gt; C211913 &gt; C91102</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
+          <t>C191069</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Head: Area Score</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>3</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>C191069 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>C191070</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Upper Extremities: Erythema/Redness</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>3</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>C191070 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>C191071</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Upper Extremities: Thickness/Induration</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>3</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>C191071 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>C191072</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Upper Extremities: Desquamation/Scaling</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>C191072 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>C191073</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Upper Extremities: Area Score</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>C191073 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>C191074</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Trunk: Erythema/Redness</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>3</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>C191074 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>C191075</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Trunk: Thickness/Induration</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>3</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>C191075 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>C191076</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Trunk: Desquamation/Scaling</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>3</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>C191076 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>C191077</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Trunk: Area Score</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>3</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>C191077 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>C191078</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Lower Extremities: Erythema/Redness</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>3</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>C191078 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>C191079</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Lower Extremities: Thickness/Induration</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>3</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>C191079 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>C191080</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Lower Extremities: Desquamation/Scaling</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>3</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>C191080 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>C191081</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>PASI Fredriksson Version - Lower Extremities: Area Score</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>3</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>C191081 &gt; C190947 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>C191153</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Rutgeerts Score - Rutgeerts Score</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>C190946</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Rutgeerts Score Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>3</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>C191153 &gt; C190946 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>C208544</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>CDISC ADAS-Cog - Total Score</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>C100106</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ADAS-Cog CDISC Version Functional Test Question</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>C91102</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Question</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>3</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>C208544 &gt; C100106 &gt; C211913 &gt; C91102</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>C222259</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Cognitive Assessment Tool</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>C222259</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Cognitive Assessment Tool</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>C222259</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>C222260</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Clinical or Research Functional Assessment Tool</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>C222260</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Clinical or Research Functional Assessment Tool</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>C222260</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>C82394</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Tanner Scale</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>C82394</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Tanner Scale</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>C82394</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>C94534</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Response in Target Lesion</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>C94534 &gt; C50995</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>C94535</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Response in Non-Target Lesion</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>C94535 &gt; C50995</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>C94536</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Best Overall Response</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>C94536 &gt; C50995</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>C96613</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Overall Response</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>C50995</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Disease Response</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>C96613 &gt; C50995</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>NEW_LZZT1</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey -  Patch Appearance</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>NEW_LZZT</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>C91105</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Questionnaire</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>NEW_LZZT1 &gt; NEW_LZZT &gt; C91105</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>NEW_LZZT2</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey -  Patch Size</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>NEW_LZZT</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>C91105</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Questionnaire</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>NEW_LZZT2 &gt; NEW_LZZT &gt; C91105</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>NEW_LZZT3</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey -  Patch Durability</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>NEW_LZZT</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>C91105</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Questionnaire</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>2</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>NEW_LZZT3 &gt; NEW_LZZT &gt; C91105</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
           <t>NEW_LZZT4</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>TTS Acceptability Survey -  Patch Acceptability</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>NEW_LZZT</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>TTS Acceptability Survey</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="E317" t="inlineStr">
         <is>
           <t>C91105</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
+      <c r="F317" t="inlineStr">
         <is>
           <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
-      <c r="G292" t="n">
+      <c r="G317" t="n">
         <v>2</v>
       </c>
-      <c r="H292" t="inlineStr">
+      <c r="H317" t="inlineStr">
         <is>
           <t>NEW_LZZT4 &gt; NEW_LZZT &gt; C91105</t>
         </is>
@@ -12252,11 +13252,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
@@ -12298,7 +13298,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -12376,336 +13376,336 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C35461</t>
+          <t>C25180</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clinical Course of Disease</t>
+          <t>Indicator</t>
         </is>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C35461</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical Course of Disease</t>
         </is>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C82394</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tanner Scale</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C83430</t>
+          <t>C82394</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Substance Use Status</t>
+          <t>Tanner Scale</t>
         </is>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C91102</t>
+          <t>C83430</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Question</t>
+          <t>Substance Use Status</t>
         </is>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C91102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Clinical or Research Assessment Question</t>
         </is>
       </c>
       <c r="C12" t="b">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C100106</t>
+          <t>C91105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADAS-Cog CDISC Version Functional Test Question</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="C13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C100109</t>
+          <t>C100106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BPRS-Anchored Clinical Classification Question</t>
+          <t>ADAS-Cog CDISC Version Functional Test Question</t>
         </is>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C100116</t>
+          <t>C100109</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KPS Scale Questionnaire Question</t>
+          <t>BPRS-Anchored Clinical Classification Question</t>
         </is>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C101869</t>
+          <t>C100116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AIMS Clinical Classification Question</t>
+          <t>KPS Scale Questionnaire Question</t>
         </is>
       </c>
       <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C101874</t>
+          <t>C101869</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ECOG Clinical Classification Question</t>
+          <t>AIMS Clinical Classification Question</t>
         </is>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C101875</t>
+          <t>C101874</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EQ-5D-5L Questionnaire Question</t>
+          <t>ECOG Clinical Classification Question</t>
         </is>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C101876</t>
+          <t>C101875</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HAMA Questionnaire Question</t>
+          <t>EQ-5D-5L Questionnaire Question</t>
         </is>
       </c>
       <c r="C19" t="b">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C112460</t>
+          <t>C101876</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KFSS Questionnaire Question</t>
+          <t>HAMA Questionnaire Question</t>
         </is>
       </c>
       <c r="C20" t="b">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C115409</t>
+          <t>C112460</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6MWT Functional Test Question</t>
+          <t>KFSS Questionnaire Question</t>
         </is>
       </c>
       <c r="C21" t="b">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C120994</t>
+          <t>C115409</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APACHE II Clinical Classification Question</t>
+          <t>6MWT Functional Test Question</t>
         </is>
       </c>
       <c r="C22" t="b">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C120996</t>
+          <t>C120994</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification Question</t>
+          <t>APACHE II Clinical Classification Question</t>
         </is>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C124689</t>
+          <t>C120996</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy Clinical Classification Question</t>
+          <t>Child-Pugh Clinical Classification Question</t>
         </is>
       </c>
       <c r="C24" t="b">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C124690</t>
+          <t>C124689</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl Clinical Classification Question</t>
+          <t>Tanner Scale-Boy Clinical Classification Question</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -12718,48 +13718,48 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C132527</t>
+          <t>C124690</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CES Questionnaire Question</t>
+          <t>Tanner Scale-Girl Clinical Classification Question</t>
         </is>
       </c>
       <c r="C26" t="b">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C135705</t>
+          <t>C132527</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CGI Generic Modification Version Questionnaire Question</t>
+          <t>CES Questionnaire Question</t>
         </is>
       </c>
       <c r="C27" t="b">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C135706</t>
+          <t>C135705</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PGI Generic Modification Version Questionnaire Question</t>
+          <t>CGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="C28" t="b">
@@ -12772,48 +13772,48 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C135706</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>PGI Generic Modification Version Questionnaire Question</t>
         </is>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C141675</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>AJCC v7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="C30" t="b">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -12826,12 +13826,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C190946</t>
+          <t>C177561</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
+          <t>AJCC Cancer Staging Manual</t>
         </is>
       </c>
       <c r="C32" t="b">
@@ -12844,36 +13844,126 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C211913</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CDISC QRS Instruments Questions</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NEW_LZZT</t>
+          <t>C190945</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TTS Acceptability Survey</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C190946</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rutgeerts Score Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C211913</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CDISC QRS Instruments Questions</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C93645</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Recurrence Indicator</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NEW_LZZT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TTS Acceptability Survey</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
         <v>4</v>
       </c>
     </row>
